--- a/StructureDefinition-ophthalmic-oct-rnfl.xlsx
+++ b/StructureDefinition-ophthalmic-oct-rnfl.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T17:13:42+00:00</t>
+    <t>2026-08-19T17:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,11 +87,11 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Represents an OCT retinal nerve fiber layer (RNFL) thickness analysis, with
-quadrant-level components and an overall classification, matching the structure of typical
-vendor reports (e.g. Heidelberg Spectralis). Real LOINC codes exist for each quadrant, but
-are laterality-specific (a different code for right vs. left eye); implementers should
-select the correct code for the eye being examined when populating each component. See
+    <t>Represents an OCT retinal nerve fiber layer (RNFL) thickness analysis, with
+quadrant-level components and an overall classification, matching the structure of typical
+vendor reports (e.g. Heidelberg Spectralis). Real LOINC codes exist for each quadrant, but
+are laterality-specific (a different code for right vs. left eye); implementers should
+select the correct code for the eye being examined when populating each component. See
 Terminology for the general LOINC-for-structured-panels strategy.</t>
   </si>
   <si>

--- a/StructureDefinition-ophthalmic-oct-rnfl.xlsx
+++ b/StructureDefinition-ophthalmic-oct-rnfl.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T00:41:24+00:00</t>
+    <t>2026-08-25T02:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-oct-rnfl.xlsx
+++ b/StructureDefinition-ophthalmic-oct-rnfl.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T02:25:39+00:00</t>
+    <t>2026-08-25T18:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-oct-rnfl.xlsx
+++ b/StructureDefinition-ophthalmic-oct-rnfl.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$289</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11062" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11215" uniqueCount="784">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T18:52:20+00:00</t>
+    <t>2026-09-01T17:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -290,7 +290,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}inv-oct-signal:OCT signal strength should be documented {component.where(code.text = 'Signal strength').exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -760,7 +760,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ophthalmic-encounter)
 </t>
   </si>
   <si>
@@ -1262,7 +1262,7 @@
 </t>
   </si>
   <si>
-    <t>(Measurement) Device</t>
+    <t>Acquisition device (manufacturer, model, software version)</t>
   </si>
   <si>
     <t>The device used to generate the observation data.</t>
@@ -2308,6 +2308,33 @@
     <t>Signal strength - quality/reliability of scan, from Cirrus (0-10)</t>
   </si>
   <si>
+    <t>Observation.component:signalStrength.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component:signalStrength.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:signalStrength.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component:signalStrength.code.text</t>
+  </si>
+  <si>
+    <t>Observation.component.code.text</t>
+  </si>
+  <si>
+    <t>Signal strength</t>
+  </si>
+  <si>
     <t>Observation.component:signalStrength.value[x]</t>
   </si>
   <si>
@@ -2338,7 +2365,7 @@
     <t>Observation.component:thicknessDef.code</t>
   </si>
   <si>
-    <t>DICOM CID 4262</t>
+    <t>Retinal thickness definition - how RNFL thickness is defined (ILM to RNFL boundary). DICOM CID 4262</t>
   </si>
   <si>
     <t>Observation.component:thicknessDef.value[x]</t>
@@ -2371,7 +2398,7 @@
     <t>Observation.component:pupilDilated.code</t>
   </si>
   <si>
-    <t>DICOM (0022,000D)</t>
+    <t>Pupil dilated - whether pupil was dilated. DICOM (0022,000D)</t>
   </si>
   <si>
     <t>Observation.component:pupilDilated.value[x]</t>
@@ -2404,7 +2431,7 @@
     <t>Observation.component:mydriaticAgent.code</t>
   </si>
   <si>
-    <t>DICOM (0022,000E)</t>
+    <t>Mydriatic agent - dilating agent used. DICOM (0022,000E)</t>
   </si>
   <si>
     <t>Observation.component:mydriaticAgent.value[x]</t>
@@ -2741,7 +2768,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP285"/>
+  <dimension ref="A1:AP289"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.7734375" customWidth="true" bestFit="true"/>
@@ -4963,7 +4990,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>233</v>
       </c>
@@ -4982,7 +5009,7 @@
         <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>83</v>
@@ -5085,7 +5112,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>244</v>
       </c>
@@ -5104,7 +5131,7 @@
         <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>83</v>
@@ -7373,7 +7400,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>394</v>
       </c>
@@ -7392,7 +7419,7 @@
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>83</v>
@@ -33608,7 +33635,7 @@
         <v>738</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>485</v>
+        <v>739</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -33628,23 +33655,19 @@
         <v>83</v>
       </c>
       <c r="J255" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>506</v>
+        <v>324</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>486</v>
+        <v>325</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N255" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O255" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N255" s="2"/>
+      <c r="O255" s="2"/>
       <c r="P255" t="s" s="2">
         <v>83</v>
       </c>
@@ -33692,7 +33715,7 @@
         <v>83</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>485</v>
+        <v>327</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>81</v>
@@ -33704,44 +33727,44 @@
         <v>83</v>
       </c>
       <c r="AJ255" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK255" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL255" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AM255" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="AN255" t="s" s="2">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="AO255" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP255" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>489</v>
+        <v>741</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E256" s="2"/>
       <c r="F256" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H256" t="s" s="2">
         <v>83</v>
@@ -33753,20 +33776,18 @@
         <v>83</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>490</v>
+        <v>141</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>491</v>
+        <v>330</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O256" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O256" s="2"/>
       <c r="P256" t="s" s="2">
         <v>83</v>
       </c>
@@ -33790,43 +33811,43 @@
         <v>83</v>
       </c>
       <c r="X256" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y256" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z256" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB256" t="s" s="2">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="AC256" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="AD256" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE256" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>489</v>
+        <v>334</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH256" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK256" t="s" s="2">
         <v>83</v>
@@ -33835,10 +33856,10 @@
         <v>83</v>
       </c>
       <c r="AM256" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN256" t="s" s="2">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="AO256" t="s" s="2">
         <v>83</v>
@@ -33849,14 +33870,14 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>493</v>
+        <v>743</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
@@ -33872,22 +33893,22 @@
         <v>83</v>
       </c>
       <c r="J257" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>192</v>
+        <v>360</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>494</v>
+        <v>361</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>296</v>
+        <v>362</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>297</v>
+        <v>363</v>
       </c>
       <c r="O257" t="s" s="2">
-        <v>298</v>
+        <v>364</v>
       </c>
       <c r="P257" t="s" s="2">
         <v>83</v>
@@ -33912,13 +33933,13 @@
         <v>83</v>
       </c>
       <c r="X257" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y257" t="s" s="2">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="Z257" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AA257" t="s" s="2">
         <v>83</v>
@@ -33936,7 +33957,7 @@
         <v>83</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>493</v>
+        <v>365</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>81</v>
@@ -33954,27 +33975,27 @@
         <v>83</v>
       </c>
       <c r="AL257" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM257" t="s" s="2">
-        <v>302</v>
+        <v>366</v>
       </c>
       <c r="AN257" t="s" s="2">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="AO257" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP257" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>495</v>
+        <v>745</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33985,7 +34006,7 @@
         <v>81</v>
       </c>
       <c r="G258" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H258" t="s" s="2">
         <v>83</v>
@@ -33994,22 +34015,22 @@
         <v>83</v>
       </c>
       <c r="J258" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>496</v>
+        <v>369</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>497</v>
+        <v>370</v>
       </c>
       <c r="N258" t="s" s="2">
-        <v>407</v>
+        <v>371</v>
       </c>
       <c r="O258" t="s" s="2">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>83</v>
@@ -34019,7 +34040,7 @@
         <v>83</v>
       </c>
       <c r="S258" t="s" s="2">
-        <v>83</v>
+        <v>746</v>
       </c>
       <c r="T258" t="s" s="2">
         <v>83</v>
@@ -34058,13 +34079,13 @@
         <v>83</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>495</v>
+        <v>373</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH258" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI258" t="s" s="2">
         <v>83</v>
@@ -34079,10 +34100,10 @@
         <v>83</v>
       </c>
       <c r="AM258" t="s" s="2">
-        <v>410</v>
+        <v>374</v>
       </c>
       <c r="AN258" t="s" s="2">
-        <v>411</v>
+        <v>375</v>
       </c>
       <c r="AO258" t="s" s="2">
         <v>83</v>
@@ -34091,16 +34112,14 @@
         <v>83</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C259" t="s" s="2">
-        <v>743</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
         <v>83</v>
       </c>
@@ -34112,7 +34131,7 @@
         <v>94</v>
       </c>
       <c r="H259" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I259" t="s" s="2">
         <v>83</v>
@@ -34121,19 +34140,19 @@
         <v>95</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>404</v>
+        <v>506</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>471</v>
+        <v>275</v>
       </c>
       <c r="N259" t="s" s="2">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="O259" t="s" s="2">
-        <v>473</v>
+        <v>277</v>
       </c>
       <c r="P259" t="s" s="2">
         <v>83</v>
@@ -34182,13 +34201,13 @@
         <v>83</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH259" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI259" t="s" s="2">
         <v>83</v>
@@ -34200,27 +34219,27 @@
         <v>83</v>
       </c>
       <c r="AL259" t="s" s="2">
-        <v>83</v>
+        <v>488</v>
       </c>
       <c r="AM259" t="s" s="2">
-        <v>475</v>
+        <v>280</v>
       </c>
       <c r="AN259" t="s" s="2">
-        <v>476</v>
+        <v>281</v>
       </c>
       <c r="AO259" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP259" t="s" s="2">
-        <v>83</v>
+        <v>282</v>
       </c>
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -34243,16 +34262,20 @@
         <v>83</v>
       </c>
       <c r="K260" t="s" s="2">
-        <v>324</v>
+        <v>192</v>
       </c>
       <c r="L260" t="s" s="2">
-        <v>325</v>
+        <v>490</v>
       </c>
       <c r="M260" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N260" s="2"/>
-      <c r="O260" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N260" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O260" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P260" t="s" s="2">
         <v>83</v>
       </c>
@@ -34276,13 +34299,13 @@
         <v>83</v>
       </c>
       <c r="X260" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="Y260" t="s" s="2">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="Z260" t="s" s="2">
-        <v>83</v>
+        <v>290</v>
       </c>
       <c r="AA260" t="s" s="2">
         <v>83</v>
@@ -34300,7 +34323,7 @@
         <v>83</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>327</v>
+        <v>489</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>81</v>
@@ -34309,10 +34332,10 @@
         <v>94</v>
       </c>
       <c r="AI260" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="AJ260" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK260" t="s" s="2">
         <v>83</v>
@@ -34321,10 +34344,10 @@
         <v>83</v>
       </c>
       <c r="AM260" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AN260" t="s" s="2">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="AO260" t="s" s="2">
         <v>83</v>
@@ -34335,14 +34358,14 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
-        <v>139</v>
+        <v>294</v>
       </c>
       <c r="E261" s="2"/>
       <c r="F261" t="s" s="2">
@@ -34361,18 +34384,20 @@
         <v>83</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>141</v>
+        <v>494</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>330</v>
+        <v>296</v>
       </c>
       <c r="N261" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O261" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="O261" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P261" t="s" s="2">
         <v>83</v>
       </c>
@@ -34396,13 +34421,13 @@
         <v>83</v>
       </c>
       <c r="X261" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="Y261" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="Z261" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="AA261" t="s" s="2">
         <v>83</v>
@@ -34420,7 +34445,7 @@
         <v>83</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>334</v>
+        <v>493</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>81</v>
@@ -34432,37 +34457,37 @@
         <v>83</v>
       </c>
       <c r="AJ261" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK261" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL261" t="s" s="2">
-        <v>83</v>
+        <v>301</v>
       </c>
       <c r="AM261" t="s" s="2">
-        <v>83</v>
+        <v>302</v>
       </c>
       <c r="AN261" t="s" s="2">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="AO261" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP261" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="E262" s="2"/>
       <c r="F262" t="s" s="2">
@@ -34475,25 +34500,25 @@
         <v>83</v>
       </c>
       <c r="I262" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J262" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>416</v>
+        <v>496</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>417</v>
+        <v>497</v>
       </c>
       <c r="N262" t="s" s="2">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="O262" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="P262" t="s" s="2">
         <v>83</v>
@@ -34542,7 +34567,7 @@
         <v>83</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>418</v>
+        <v>495</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>81</v>
@@ -34554,7 +34579,7 @@
         <v>83</v>
       </c>
       <c r="AJ262" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK262" t="s" s="2">
         <v>83</v>
@@ -34563,10 +34588,10 @@
         <v>83</v>
       </c>
       <c r="AM262" t="s" s="2">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="AN262" t="s" s="2">
-        <v>137</v>
+        <v>411</v>
       </c>
       <c r="AO262" t="s" s="2">
         <v>83</v>
@@ -34575,26 +34600,28 @@
         <v>83</v>
       </c>
     </row>
-    <row r="263" hidden="true">
+    <row r="263">
       <c r="A263" t="s" s="2">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C263" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="C263" t="s" s="2">
+        <v>752</v>
+      </c>
       <c r="D263" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E263" s="2"/>
       <c r="F263" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G263" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H263" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I263" t="s" s="2">
         <v>83</v>
@@ -34603,19 +34630,19 @@
         <v>95</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>192</v>
+        <v>404</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>748</v>
+        <v>470</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="N263" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="O263" t="s" s="2">
-        <v>207</v>
+        <v>473</v>
       </c>
       <c r="P263" t="s" s="2">
         <v>83</v>
@@ -34640,13 +34667,13 @@
         <v>83</v>
       </c>
       <c r="X263" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y263" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z263" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA263" t="s" s="2">
         <v>83</v>
@@ -34664,13 +34691,13 @@
         <v>83</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AG263" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH263" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI263" t="s" s="2">
         <v>83</v>
@@ -34682,16 +34709,16 @@
         <v>83</v>
       </c>
       <c r="AL263" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>213</v>
+        <v>475</v>
       </c>
       <c r="AN263" t="s" s="2">
-        <v>214</v>
+        <v>476</v>
       </c>
       <c r="AO263" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP263" t="s" s="2">
         <v>83</v>
@@ -34699,10 +34726,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -34722,23 +34749,19 @@
         <v>83</v>
       </c>
       <c r="J264" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>192</v>
+        <v>324</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>486</v>
+        <v>325</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N264" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O264" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N264" s="2"/>
+      <c r="O264" s="2"/>
       <c r="P264" t="s" s="2">
         <v>83</v>
       </c>
@@ -34786,7 +34809,7 @@
         <v>83</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>485</v>
+        <v>327</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>81</v>
@@ -34798,44 +34821,44 @@
         <v>83</v>
       </c>
       <c r="AJ264" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK264" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL264" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AM264" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="AN264" t="s" s="2">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="AO264" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP264" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E265" s="2"/>
       <c r="F265" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G265" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H265" t="s" s="2">
         <v>83</v>
@@ -34847,20 +34870,18 @@
         <v>83</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>490</v>
+        <v>141</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>491</v>
+        <v>330</v>
       </c>
       <c r="N265" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O265" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O265" s="2"/>
       <c r="P265" t="s" s="2">
         <v>83</v>
       </c>
@@ -34884,13 +34905,13 @@
         <v>83</v>
       </c>
       <c r="X265" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y265" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z265" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>83</v>
@@ -34908,19 +34929,19 @@
         <v>83</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>489</v>
+        <v>334</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH265" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI265" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ265" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK265" t="s" s="2">
         <v>83</v>
@@ -34929,10 +34950,10 @@
         <v>83</v>
       </c>
       <c r="AM265" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN265" t="s" s="2">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="AO265" t="s" s="2">
         <v>83</v>
@@ -34943,14 +34964,14 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
-        <v>294</v>
+        <v>415</v>
       </c>
       <c r="E266" s="2"/>
       <c r="F266" t="s" s="2">
@@ -34963,25 +34984,25 @@
         <v>83</v>
       </c>
       <c r="I266" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J266" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>494</v>
+        <v>416</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>296</v>
+        <v>417</v>
       </c>
       <c r="N266" t="s" s="2">
-        <v>297</v>
+        <v>143</v>
       </c>
       <c r="O266" t="s" s="2">
-        <v>298</v>
+        <v>149</v>
       </c>
       <c r="P266" t="s" s="2">
         <v>83</v>
@@ -35006,13 +35027,13 @@
         <v>83</v>
       </c>
       <c r="X266" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y266" t="s" s="2">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="Z266" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>83</v>
@@ -35030,7 +35051,7 @@
         <v>83</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>493</v>
+        <v>418</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>81</v>
@@ -35042,33 +35063,33 @@
         <v>83</v>
       </c>
       <c r="AJ266" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK266" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL266" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM266" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="AN266" t="s" s="2">
-        <v>303</v>
+        <v>137</v>
       </c>
       <c r="AO266" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP266" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -35076,10 +35097,10 @@
       </c>
       <c r="E267" s="2"/>
       <c r="F267" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G267" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H267" t="s" s="2">
         <v>83</v>
@@ -35088,22 +35109,22 @@
         <v>83</v>
       </c>
       <c r="J267" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>496</v>
+        <v>757</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="N267" t="s" s="2">
-        <v>407</v>
+        <v>483</v>
       </c>
       <c r="O267" t="s" s="2">
-        <v>408</v>
+        <v>207</v>
       </c>
       <c r="P267" t="s" s="2">
         <v>83</v>
@@ -35128,13 +35149,13 @@
         <v>83</v>
       </c>
       <c r="X267" t="s" s="2">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="Y267" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="Z267" t="s" s="2">
-        <v>83</v>
+        <v>210</v>
       </c>
       <c r="AA267" t="s" s="2">
         <v>83</v>
@@ -35152,13 +35173,13 @@
         <v>83</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="AG267" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH267" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI267" t="s" s="2">
         <v>83</v>
@@ -35170,31 +35191,29 @@
         <v>83</v>
       </c>
       <c r="AL267" t="s" s="2">
-        <v>83</v>
+        <v>484</v>
       </c>
       <c r="AM267" t="s" s="2">
-        <v>410</v>
+        <v>213</v>
       </c>
       <c r="AN267" t="s" s="2">
-        <v>411</v>
+        <v>214</v>
       </c>
       <c r="AO267" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AP267" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C268" t="s" s="2">
-        <v>754</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
         <v>83</v>
       </c>
@@ -35206,7 +35225,7 @@
         <v>94</v>
       </c>
       <c r="H268" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I268" t="s" s="2">
         <v>83</v>
@@ -35215,19 +35234,19 @@
         <v>95</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>404</v>
+        <v>192</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>471</v>
+        <v>275</v>
       </c>
       <c r="N268" t="s" s="2">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="O268" t="s" s="2">
-        <v>473</v>
+        <v>277</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>83</v>
@@ -35276,13 +35295,13 @@
         <v>83</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH268" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI268" t="s" s="2">
         <v>83</v>
@@ -35294,27 +35313,27 @@
         <v>83</v>
       </c>
       <c r="AL268" t="s" s="2">
-        <v>83</v>
+        <v>488</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>475</v>
+        <v>280</v>
       </c>
       <c r="AN268" t="s" s="2">
-        <v>476</v>
+        <v>281</v>
       </c>
       <c r="AO268" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP268" t="s" s="2">
-        <v>83</v>
+        <v>282</v>
       </c>
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -35337,16 +35356,20 @@
         <v>83</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>324</v>
+        <v>192</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>325</v>
+        <v>490</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N269" s="2"/>
-      <c r="O269" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N269" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O269" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P269" t="s" s="2">
         <v>83</v>
       </c>
@@ -35370,13 +35393,13 @@
         <v>83</v>
       </c>
       <c r="X269" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="Y269" t="s" s="2">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="Z269" t="s" s="2">
-        <v>83</v>
+        <v>290</v>
       </c>
       <c r="AA269" t="s" s="2">
         <v>83</v>
@@ -35394,7 +35417,7 @@
         <v>83</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>327</v>
+        <v>489</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>81</v>
@@ -35403,10 +35426,10 @@
         <v>94</v>
       </c>
       <c r="AI269" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="AJ269" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK269" t="s" s="2">
         <v>83</v>
@@ -35415,10 +35438,10 @@
         <v>83</v>
       </c>
       <c r="AM269" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AN269" t="s" s="2">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="AO269" t="s" s="2">
         <v>83</v>
@@ -35429,14 +35452,14 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
-        <v>139</v>
+        <v>294</v>
       </c>
       <c r="E270" s="2"/>
       <c r="F270" t="s" s="2">
@@ -35455,18 +35478,20 @@
         <v>83</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>141</v>
+        <v>494</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>330</v>
+        <v>296</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O270" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="O270" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P270" t="s" s="2">
         <v>83</v>
       </c>
@@ -35490,13 +35515,13 @@
         <v>83</v>
       </c>
       <c r="X270" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="Y270" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="Z270" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="AA270" t="s" s="2">
         <v>83</v>
@@ -35514,7 +35539,7 @@
         <v>83</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>334</v>
+        <v>493</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>81</v>
@@ -35526,37 +35551,37 @@
         <v>83</v>
       </c>
       <c r="AJ270" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK270" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL270" t="s" s="2">
-        <v>83</v>
+        <v>301</v>
       </c>
       <c r="AM270" t="s" s="2">
-        <v>83</v>
+        <v>302</v>
       </c>
       <c r="AN270" t="s" s="2">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="AO270" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP270" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="E271" s="2"/>
       <c r="F271" t="s" s="2">
@@ -35569,25 +35594,25 @@
         <v>83</v>
       </c>
       <c r="I271" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J271" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>416</v>
+        <v>496</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>417</v>
+        <v>497</v>
       </c>
       <c r="N271" t="s" s="2">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="O271" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="P271" t="s" s="2">
         <v>83</v>
@@ -35636,7 +35661,7 @@
         <v>83</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>418</v>
+        <v>495</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>81</v>
@@ -35648,7 +35673,7 @@
         <v>83</v>
       </c>
       <c r="AJ271" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK271" t="s" s="2">
         <v>83</v>
@@ -35657,10 +35682,10 @@
         <v>83</v>
       </c>
       <c r="AM271" t="s" s="2">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="AN271" t="s" s="2">
-        <v>137</v>
+        <v>411</v>
       </c>
       <c r="AO271" t="s" s="2">
         <v>83</v>
@@ -35669,26 +35694,28 @@
         <v>83</v>
       </c>
     </row>
-    <row r="272" hidden="true">
+    <row r="272">
       <c r="A272" t="s" s="2">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C272" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="C272" t="s" s="2">
+        <v>763</v>
+      </c>
       <c r="D272" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E272" s="2"/>
       <c r="F272" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G272" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H272" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I272" t="s" s="2">
         <v>83</v>
@@ -35697,19 +35724,19 @@
         <v>95</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>192</v>
+        <v>404</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>759</v>
+        <v>470</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="N272" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="O272" t="s" s="2">
-        <v>207</v>
+        <v>473</v>
       </c>
       <c r="P272" t="s" s="2">
         <v>83</v>
@@ -35734,13 +35761,13 @@
         <v>83</v>
       </c>
       <c r="X272" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y272" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z272" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA272" t="s" s="2">
         <v>83</v>
@@ -35758,13 +35785,13 @@
         <v>83</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AG272" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH272" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI272" t="s" s="2">
         <v>83</v>
@@ -35776,16 +35803,16 @@
         <v>83</v>
       </c>
       <c r="AL272" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM272" t="s" s="2">
-        <v>213</v>
+        <v>475</v>
       </c>
       <c r="AN272" t="s" s="2">
-        <v>214</v>
+        <v>476</v>
       </c>
       <c r="AO272" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP272" t="s" s="2">
         <v>83</v>
@@ -35793,10 +35820,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -35816,23 +35843,19 @@
         <v>83</v>
       </c>
       <c r="J273" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>192</v>
+        <v>324</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>486</v>
+        <v>325</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N273" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O273" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N273" s="2"/>
+      <c r="O273" s="2"/>
       <c r="P273" t="s" s="2">
         <v>83</v>
       </c>
@@ -35880,7 +35903,7 @@
         <v>83</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>485</v>
+        <v>327</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>81</v>
@@ -35892,44 +35915,44 @@
         <v>83</v>
       </c>
       <c r="AJ273" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK273" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL273" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AM273" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="AN273" t="s" s="2">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="AO273" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP273" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E274" s="2"/>
       <c r="F274" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G274" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H274" t="s" s="2">
         <v>83</v>
@@ -35941,20 +35964,18 @@
         <v>83</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>490</v>
+        <v>141</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>491</v>
+        <v>330</v>
       </c>
       <c r="N274" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O274" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O274" s="2"/>
       <c r="P274" t="s" s="2">
         <v>83</v>
       </c>
@@ -35978,13 +35999,13 @@
         <v>83</v>
       </c>
       <c r="X274" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y274" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z274" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA274" t="s" s="2">
         <v>83</v>
@@ -36002,19 +36023,19 @@
         <v>83</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>489</v>
+        <v>334</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH274" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI274" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ274" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK274" t="s" s="2">
         <v>83</v>
@@ -36023,10 +36044,10 @@
         <v>83</v>
       </c>
       <c r="AM274" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN274" t="s" s="2">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="AO274" t="s" s="2">
         <v>83</v>
@@ -36037,14 +36058,14 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
-        <v>294</v>
+        <v>415</v>
       </c>
       <c r="E275" s="2"/>
       <c r="F275" t="s" s="2">
@@ -36057,25 +36078,25 @@
         <v>83</v>
       </c>
       <c r="I275" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J275" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>494</v>
+        <v>416</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>296</v>
+        <v>417</v>
       </c>
       <c r="N275" t="s" s="2">
-        <v>297</v>
+        <v>143</v>
       </c>
       <c r="O275" t="s" s="2">
-        <v>298</v>
+        <v>149</v>
       </c>
       <c r="P275" t="s" s="2">
         <v>83</v>
@@ -36100,13 +36121,13 @@
         <v>83</v>
       </c>
       <c r="X275" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y275" t="s" s="2">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="Z275" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AA275" t="s" s="2">
         <v>83</v>
@@ -36124,7 +36145,7 @@
         <v>83</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>493</v>
+        <v>418</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>81</v>
@@ -36136,33 +36157,33 @@
         <v>83</v>
       </c>
       <c r="AJ275" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK275" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL275" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM275" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="AN275" t="s" s="2">
-        <v>303</v>
+        <v>137</v>
       </c>
       <c r="AO275" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP275" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -36170,10 +36191,10 @@
       </c>
       <c r="E276" s="2"/>
       <c r="F276" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G276" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H276" t="s" s="2">
         <v>83</v>
@@ -36182,22 +36203,22 @@
         <v>83</v>
       </c>
       <c r="J276" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>496</v>
+        <v>768</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>407</v>
+        <v>483</v>
       </c>
       <c r="O276" t="s" s="2">
-        <v>408</v>
+        <v>207</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>83</v>
@@ -36222,13 +36243,13 @@
         <v>83</v>
       </c>
       <c r="X276" t="s" s="2">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="Y276" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="Z276" t="s" s="2">
-        <v>83</v>
+        <v>210</v>
       </c>
       <c r="AA276" t="s" s="2">
         <v>83</v>
@@ -36246,13 +36267,13 @@
         <v>83</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="AG276" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH276" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI276" t="s" s="2">
         <v>83</v>
@@ -36264,31 +36285,29 @@
         <v>83</v>
       </c>
       <c r="AL276" t="s" s="2">
-        <v>83</v>
+        <v>484</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>410</v>
+        <v>213</v>
       </c>
       <c r="AN276" t="s" s="2">
-        <v>411</v>
+        <v>214</v>
       </c>
       <c r="AO276" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AP276" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C277" t="s" s="2">
-        <v>765</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
         <v>83</v>
       </c>
@@ -36300,7 +36319,7 @@
         <v>94</v>
       </c>
       <c r="H277" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I277" t="s" s="2">
         <v>83</v>
@@ -36309,19 +36328,19 @@
         <v>95</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>404</v>
+        <v>192</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>471</v>
+        <v>275</v>
       </c>
       <c r="N277" t="s" s="2">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="O277" t="s" s="2">
-        <v>473</v>
+        <v>277</v>
       </c>
       <c r="P277" t="s" s="2">
         <v>83</v>
@@ -36370,13 +36389,13 @@
         <v>83</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH277" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI277" t="s" s="2">
         <v>83</v>
@@ -36388,27 +36407,27 @@
         <v>83</v>
       </c>
       <c r="AL277" t="s" s="2">
-        <v>83</v>
+        <v>488</v>
       </c>
       <c r="AM277" t="s" s="2">
-        <v>475</v>
+        <v>280</v>
       </c>
       <c r="AN277" t="s" s="2">
-        <v>476</v>
+        <v>281</v>
       </c>
       <c r="AO277" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP277" t="s" s="2">
-        <v>83</v>
+        <v>282</v>
       </c>
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -36431,16 +36450,20 @@
         <v>83</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>324</v>
+        <v>192</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>325</v>
+        <v>490</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N278" s="2"/>
-      <c r="O278" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N278" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O278" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P278" t="s" s="2">
         <v>83</v>
       </c>
@@ -36464,13 +36487,13 @@
         <v>83</v>
       </c>
       <c r="X278" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="Y278" t="s" s="2">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="Z278" t="s" s="2">
-        <v>83</v>
+        <v>290</v>
       </c>
       <c r="AA278" t="s" s="2">
         <v>83</v>
@@ -36488,7 +36511,7 @@
         <v>83</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>327</v>
+        <v>489</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>81</v>
@@ -36497,10 +36520,10 @@
         <v>94</v>
       </c>
       <c r="AI278" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="AJ278" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK278" t="s" s="2">
         <v>83</v>
@@ -36509,10 +36532,10 @@
         <v>83</v>
       </c>
       <c r="AM278" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AN278" t="s" s="2">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="AO278" t="s" s="2">
         <v>83</v>
@@ -36523,14 +36546,14 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
-        <v>139</v>
+        <v>294</v>
       </c>
       <c r="E279" s="2"/>
       <c r="F279" t="s" s="2">
@@ -36549,18 +36572,20 @@
         <v>83</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>141</v>
+        <v>494</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>330</v>
+        <v>296</v>
       </c>
       <c r="N279" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O279" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="O279" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P279" t="s" s="2">
         <v>83</v>
       </c>
@@ -36584,13 +36609,13 @@
         <v>83</v>
       </c>
       <c r="X279" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="Y279" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="Z279" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="AA279" t="s" s="2">
         <v>83</v>
@@ -36608,7 +36633,7 @@
         <v>83</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>334</v>
+        <v>493</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>81</v>
@@ -36620,37 +36645,37 @@
         <v>83</v>
       </c>
       <c r="AJ279" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK279" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL279" t="s" s="2">
-        <v>83</v>
+        <v>301</v>
       </c>
       <c r="AM279" t="s" s="2">
-        <v>83</v>
+        <v>302</v>
       </c>
       <c r="AN279" t="s" s="2">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="AO279" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP279" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="E280" s="2"/>
       <c r="F280" t="s" s="2">
@@ -36663,25 +36688,25 @@
         <v>83</v>
       </c>
       <c r="I280" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J280" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>416</v>
+        <v>496</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>417</v>
+        <v>497</v>
       </c>
       <c r="N280" t="s" s="2">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="O280" t="s" s="2">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="P280" t="s" s="2">
         <v>83</v>
@@ -36730,7 +36755,7 @@
         <v>83</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>418</v>
+        <v>495</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>81</v>
@@ -36742,7 +36767,7 @@
         <v>83</v>
       </c>
       <c r="AJ280" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK280" t="s" s="2">
         <v>83</v>
@@ -36751,10 +36776,10 @@
         <v>83</v>
       </c>
       <c r="AM280" t="s" s="2">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="AN280" t="s" s="2">
-        <v>137</v>
+        <v>411</v>
       </c>
       <c r="AO280" t="s" s="2">
         <v>83</v>
@@ -36763,26 +36788,28 @@
         <v>83</v>
       </c>
     </row>
-    <row r="281" hidden="true">
+    <row r="281">
       <c r="A281" t="s" s="2">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C281" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="C281" t="s" s="2">
+        <v>774</v>
+      </c>
       <c r="D281" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E281" s="2"/>
       <c r="F281" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G281" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H281" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I281" t="s" s="2">
         <v>83</v>
@@ -36791,19 +36818,19 @@
         <v>95</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>192</v>
+        <v>404</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>770</v>
+        <v>470</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="N281" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="O281" t="s" s="2">
-        <v>207</v>
+        <v>473</v>
       </c>
       <c r="P281" t="s" s="2">
         <v>83</v>
@@ -36828,13 +36855,13 @@
         <v>83</v>
       </c>
       <c r="X281" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y281" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z281" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA281" t="s" s="2">
         <v>83</v>
@@ -36852,13 +36879,13 @@
         <v>83</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AG281" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH281" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI281" t="s" s="2">
         <v>83</v>
@@ -36870,16 +36897,16 @@
         <v>83</v>
       </c>
       <c r="AL281" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AM281" t="s" s="2">
-        <v>213</v>
+        <v>475</v>
       </c>
       <c r="AN281" t="s" s="2">
-        <v>214</v>
+        <v>476</v>
       </c>
       <c r="AO281" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP281" t="s" s="2">
         <v>83</v>
@@ -36887,10 +36914,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -36910,23 +36937,19 @@
         <v>83</v>
       </c>
       <c r="J282" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>192</v>
+        <v>324</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>486</v>
+        <v>325</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N282" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O282" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N282" s="2"/>
+      <c r="O282" s="2"/>
       <c r="P282" t="s" s="2">
         <v>83</v>
       </c>
@@ -36974,7 +36997,7 @@
         <v>83</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>485</v>
+        <v>327</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>81</v>
@@ -36986,44 +37009,44 @@
         <v>83</v>
       </c>
       <c r="AJ282" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK282" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL282" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AM282" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="AN282" t="s" s="2">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="AO282" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP282" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E283" s="2"/>
       <c r="F283" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G283" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H283" t="s" s="2">
         <v>83</v>
@@ -37035,20 +37058,18 @@
         <v>83</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L283" t="s" s="2">
-        <v>490</v>
+        <v>141</v>
       </c>
       <c r="M283" t="s" s="2">
-        <v>491</v>
+        <v>330</v>
       </c>
       <c r="N283" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O283" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O283" s="2"/>
       <c r="P283" t="s" s="2">
         <v>83</v>
       </c>
@@ -37072,13 +37093,13 @@
         <v>83</v>
       </c>
       <c r="X283" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y283" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z283" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA283" t="s" s="2">
         <v>83</v>
@@ -37096,19 +37117,19 @@
         <v>83</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>489</v>
+        <v>334</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH283" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI283" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ283" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK283" t="s" s="2">
         <v>83</v>
@@ -37117,10 +37138,10 @@
         <v>83</v>
       </c>
       <c r="AM283" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN283" t="s" s="2">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="AO283" t="s" s="2">
         <v>83</v>
@@ -37131,14 +37152,14 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
-        <v>294</v>
+        <v>415</v>
       </c>
       <c r="E284" s="2"/>
       <c r="F284" t="s" s="2">
@@ -37151,25 +37172,25 @@
         <v>83</v>
       </c>
       <c r="I284" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J284" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K284" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>494</v>
+        <v>416</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>296</v>
+        <v>417</v>
       </c>
       <c r="N284" t="s" s="2">
-        <v>297</v>
+        <v>143</v>
       </c>
       <c r="O284" t="s" s="2">
-        <v>298</v>
+        <v>149</v>
       </c>
       <c r="P284" t="s" s="2">
         <v>83</v>
@@ -37194,13 +37215,13 @@
         <v>83</v>
       </c>
       <c r="X284" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y284" t="s" s="2">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="Z284" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AA284" t="s" s="2">
         <v>83</v>
@@ -37218,7 +37239,7 @@
         <v>83</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>493</v>
+        <v>418</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>81</v>
@@ -37230,33 +37251,33 @@
         <v>83</v>
       </c>
       <c r="AJ284" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK284" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL284" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM284" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="AN284" t="s" s="2">
-        <v>303</v>
+        <v>137</v>
       </c>
       <c r="AO284" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP284" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -37264,10 +37285,10 @@
       </c>
       <c r="E285" s="2"/>
       <c r="F285" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G285" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H285" t="s" s="2">
         <v>83</v>
@@ -37276,22 +37297,22 @@
         <v>83</v>
       </c>
       <c r="J285" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>496</v>
+        <v>779</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="N285" t="s" s="2">
-        <v>407</v>
+        <v>483</v>
       </c>
       <c r="O285" t="s" s="2">
-        <v>408</v>
+        <v>207</v>
       </c>
       <c r="P285" t="s" s="2">
         <v>83</v>
@@ -37316,13 +37337,13 @@
         <v>83</v>
       </c>
       <c r="X285" t="s" s="2">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="Y285" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="Z285" t="s" s="2">
-        <v>83</v>
+        <v>210</v>
       </c>
       <c r="AA285" t="s" s="2">
         <v>83</v>
@@ -37340,13 +37361,13 @@
         <v>83</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="AG285" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH285" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI285" t="s" s="2">
         <v>83</v>
@@ -37358,23 +37379,511 @@
         <v>83</v>
       </c>
       <c r="AL285" t="s" s="2">
-        <v>83</v>
+        <v>484</v>
       </c>
       <c r="AM285" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AN285" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AO285" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AP285" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="286" hidden="true">
+      <c r="A286" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B286" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C286" s="2"/>
+      <c r="D286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E286" s="2"/>
+      <c r="F286" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G286" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J286" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K286" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L286" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M286" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N286" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O286" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="P286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q286" s="2"/>
+      <c r="R286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF286" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG286" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH286" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ286" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL286" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM286" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AN286" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AO286" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP286" t="s" s="2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="287" hidden="true">
+      <c r="A287" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="B287" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C287" s="2"/>
+      <c r="D287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E287" s="2"/>
+      <c r="F287" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G287" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K287" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L287" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M287" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N287" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O287" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="P287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q287" s="2"/>
+      <c r="R287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X287" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Y287" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Z287" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AA287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF287" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG287" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH287" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI287" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AJ287" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM287" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN287" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AO287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP287" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="288" hidden="true">
+      <c r="A288" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="B288" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C288" s="2"/>
+      <c r="D288" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="E288" s="2"/>
+      <c r="F288" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G288" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K288" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L288" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M288" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N288" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O288" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q288" s="2"/>
+      <c r="R288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X288" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Y288" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="Z288" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AA288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF288" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG288" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH288" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ288" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL288" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM288" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN288" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AO288" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP288" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="289" hidden="true">
+      <c r="A289" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="B289" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C289" s="2"/>
+      <c r="D289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E289" s="2"/>
+      <c r="F289" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G289" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K289" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L289" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M289" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N289" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O289" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="P289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q289" s="2"/>
+      <c r="R289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF289" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG289" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH289" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ289" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM289" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AN285" t="s" s="2">
+      <c r="AN289" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AO285" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP285" t="s" s="2">
+      <c r="AO289" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP289" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP285">
+  <autoFilter ref="A1:AP289">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -37384,7 +37893,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI284">
+  <conditionalFormatting sqref="A2:AI288">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
